--- a/Courses/Term 3/QAM-III/Case Studies/1440-1 DA.. DATA - keep or sell my Hyundai MBA 2025.xlsx
+++ b/Courses/Term 3/QAM-III/Case Studies/1440-1 DA.. DATA - keep or sell my Hyundai MBA 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suranjandas/Desktop/TEMP/Sent After class Delhi EMBA 98/S6 - OR z DA/sent before class DA - 80 series/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\QAM-III\Case Studies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2CAE15-73DF-B24B-9D78-0E9963ECA478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6198304-39B8-43DF-9E60-98AE80E7F709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" tabRatio="914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DA Cars" sheetId="16" r:id="rId1"/>
@@ -643,14 +643,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F155A933-E0B4-BD49-8FB0-242EAFE9D5A9}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="182" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="181.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
